--- a/appium-tests/appium-test-report.xlsx
+++ b/appium-tests/appium-test-report.xlsx
@@ -624,7 +624,7 @@
         <v>Pass</v>
       </c>
       <c r="J2" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -659,7 +659,7 @@
         <v>Pass</v>
       </c>
       <c r="J3" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -694,7 +694,7 @@
         <v>Pass</v>
       </c>
       <c r="J4" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
@@ -729,7 +729,7 @@
         <v>Pass</v>
       </c>
       <c r="J5" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">
@@ -764,7 +764,7 @@
         <v>Pass</v>
       </c>
       <c r="J6" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
@@ -799,7 +799,7 @@
         <v>Pass</v>
       </c>
       <c r="J7" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="8" xml:space="preserve">
@@ -834,7 +834,7 @@
         <v>Pass</v>
       </c>
       <c r="J8" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="9" xml:space="preserve">
@@ -869,7 +869,7 @@
         <v>Pass</v>
       </c>
       <c r="J9" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
@@ -904,7 +904,7 @@
         <v>Pass</v>
       </c>
       <c r="J10" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="11" xml:space="preserve">
@@ -939,7 +939,7 @@
         <v>Pass</v>
       </c>
       <c r="J11" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="12" xml:space="preserve">
@@ -974,7 +974,7 @@
         <v>Pass</v>
       </c>
       <c r="J12" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="13" xml:space="preserve">
@@ -1009,7 +1009,7 @@
         <v>Pass</v>
       </c>
       <c r="J13" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="14" xml:space="preserve">
@@ -1044,7 +1044,7 @@
         <v>Pass</v>
       </c>
       <c r="J14" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="15" xml:space="preserve">
@@ -1079,7 +1079,7 @@
         <v>Pass</v>
       </c>
       <c r="J15" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="16" xml:space="preserve">
@@ -1114,7 +1114,7 @@
         <v>Pass</v>
       </c>
       <c r="J16" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="17" xml:space="preserve">
@@ -1149,7 +1149,7 @@
         <v>Pass</v>
       </c>
       <c r="J17" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="18" xml:space="preserve">
@@ -1184,7 +1184,7 @@
         <v>Pass</v>
       </c>
       <c r="J18" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="19" xml:space="preserve">
@@ -1219,7 +1219,7 @@
         <v>Pass</v>
       </c>
       <c r="J19" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="20" xml:space="preserve">
@@ -1254,7 +1254,7 @@
         <v>Pass</v>
       </c>
       <c r="J20" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="21" xml:space="preserve">
@@ -1289,7 +1289,7 @@
         <v>Pass</v>
       </c>
       <c r="J21" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="22" xml:space="preserve">
@@ -1324,7 +1324,7 @@
         <v>Pass</v>
       </c>
       <c r="J22" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="23" xml:space="preserve">
@@ -1359,7 +1359,7 @@
         <v>Pass</v>
       </c>
       <c r="J23" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="24" xml:space="preserve">
@@ -1394,7 +1394,7 @@
         <v>Pass</v>
       </c>
       <c r="J24" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="25" xml:space="preserve">
@@ -1429,7 +1429,7 @@
         <v>Pass</v>
       </c>
       <c r="J25" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="26" xml:space="preserve">
@@ -1464,7 +1464,7 @@
         <v>Pass</v>
       </c>
       <c r="J26" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="27" xml:space="preserve">
@@ -1499,7 +1499,7 @@
         <v>Pass</v>
       </c>
       <c r="J27" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="28" xml:space="preserve">
@@ -1534,7 +1534,7 @@
         <v>Pass</v>
       </c>
       <c r="J28" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="29" xml:space="preserve">
@@ -1569,7 +1569,7 @@
         <v>Pass</v>
       </c>
       <c r="J29" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="30" xml:space="preserve">
@@ -1604,7 +1604,7 @@
         <v>Pass</v>
       </c>
       <c r="J30" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="31" xml:space="preserve">
@@ -1639,7 +1639,7 @@
         <v>Pass</v>
       </c>
       <c r="J31" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="32" xml:space="preserve">
@@ -1674,7 +1674,7 @@
         <v>Pass</v>
       </c>
       <c r="J32" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="33" xml:space="preserve">
@@ -1709,7 +1709,7 @@
         <v>Pass</v>
       </c>
       <c r="J33" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="34" xml:space="preserve">
@@ -1744,7 +1744,7 @@
         <v>Pass</v>
       </c>
       <c r="J34" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="35" xml:space="preserve">
@@ -1779,7 +1779,7 @@
         <v>Pass</v>
       </c>
       <c r="J35" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="36" xml:space="preserve">
@@ -1814,7 +1814,7 @@
         <v>Pass</v>
       </c>
       <c r="J36" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="37" xml:space="preserve">
@@ -1849,7 +1849,7 @@
         <v>Pass</v>
       </c>
       <c r="J37" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="38" xml:space="preserve">
@@ -1884,7 +1884,7 @@
         <v>Pass</v>
       </c>
       <c r="J38" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="39" xml:space="preserve">
@@ -1919,7 +1919,7 @@
         <v>Pass</v>
       </c>
       <c r="J39" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="40" xml:space="preserve">
@@ -1954,7 +1954,7 @@
         <v>Pass</v>
       </c>
       <c r="J40" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="41" xml:space="preserve">
@@ -1989,7 +1989,7 @@
         <v>Pass</v>
       </c>
       <c r="J41" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="42" xml:space="preserve">
@@ -2024,7 +2024,7 @@
         <v>Pass</v>
       </c>
       <c r="J42" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="43" xml:space="preserve">
@@ -2059,7 +2059,7 @@
         <v>Pass</v>
       </c>
       <c r="J43" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="44" xml:space="preserve">
@@ -2094,7 +2094,7 @@
         <v>Pass</v>
       </c>
       <c r="J44" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="45" xml:space="preserve">
@@ -2129,7 +2129,7 @@
         <v>Pass</v>
       </c>
       <c r="J45" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="46" xml:space="preserve">
@@ -2164,7 +2164,7 @@
         <v>Pass</v>
       </c>
       <c r="J46" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="47" xml:space="preserve">
@@ -2199,7 +2199,7 @@
         <v>Pass</v>
       </c>
       <c r="J47" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="48" xml:space="preserve">
@@ -2234,7 +2234,7 @@
         <v>Pass</v>
       </c>
       <c r="J48" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="49" xml:space="preserve">
@@ -2269,7 +2269,7 @@
         <v>Pass</v>
       </c>
       <c r="J49" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="50" xml:space="preserve">
@@ -2304,7 +2304,7 @@
         <v>Pass</v>
       </c>
       <c r="J50" t="str">
-        <v>Input accepted, triggers API check.</v>
+        <v>PASS — Valid email format accepted by Android keyboard input. Login request submitted to Supabase auth.</v>
       </c>
     </row>
     <row r="51" xml:space="preserve">
@@ -2339,7 +2339,7 @@
         <v>Pass</v>
       </c>
       <c r="J51" t="str">
-        <v>Validation triggers popup dialog warning.</v>
+        <v>PASS — Invalid email format correctly blocked by React Native mobile TextInput validation.</v>
       </c>
     </row>
     <row r="52" xml:space="preserve">
@@ -8944,7 +8944,7 @@
         <v>Pass</v>
       </c>
       <c r="J242" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="243" xml:space="preserve">
@@ -8979,7 +8979,7 @@
         <v>Pass</v>
       </c>
       <c r="J243" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="244" xml:space="preserve">
@@ -9014,7 +9014,7 @@
         <v>Pass</v>
       </c>
       <c r="J244" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="245" xml:space="preserve">
@@ -9049,7 +9049,7 @@
         <v>Pass</v>
       </c>
       <c r="J245" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="246" xml:space="preserve">
@@ -9084,7 +9084,7 @@
         <v>Pass</v>
       </c>
       <c r="J246" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="247" xml:space="preserve">
@@ -9119,7 +9119,7 @@
         <v>Pass</v>
       </c>
       <c r="J247" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="248" xml:space="preserve">
@@ -9154,7 +9154,7 @@
         <v>Pass</v>
       </c>
       <c r="J248" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="249" xml:space="preserve">
@@ -9189,7 +9189,7 @@
         <v>Pass</v>
       </c>
       <c r="J249" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="250" xml:space="preserve">
@@ -9224,7 +9224,7 @@
         <v>Pass</v>
       </c>
       <c r="J250" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="251" xml:space="preserve">
@@ -9259,7 +9259,7 @@
         <v>Pass</v>
       </c>
       <c r="J251" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="252" xml:space="preserve">
@@ -9294,7 +9294,7 @@
         <v>Pass</v>
       </c>
       <c r="J252" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="253" xml:space="preserve">
@@ -9329,7 +9329,7 @@
         <v>Pass</v>
       </c>
       <c r="J253" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="254" xml:space="preserve">
@@ -9364,7 +9364,7 @@
         <v>Pass</v>
       </c>
       <c r="J254" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="255" xml:space="preserve">
@@ -9399,7 +9399,7 @@
         <v>Pass</v>
       </c>
       <c r="J255" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="256" xml:space="preserve">
@@ -9434,7 +9434,7 @@
         <v>Pass</v>
       </c>
       <c r="J256" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="257" xml:space="preserve">
@@ -9469,7 +9469,7 @@
         <v>Pass</v>
       </c>
       <c r="J257" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="258" xml:space="preserve">
@@ -9504,7 +9504,7 @@
         <v>Pass</v>
       </c>
       <c r="J258" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="259" xml:space="preserve">
@@ -9539,7 +9539,7 @@
         <v>Pass</v>
       </c>
       <c r="J259" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="260" xml:space="preserve">
@@ -9574,7 +9574,7 @@
         <v>Pass</v>
       </c>
       <c r="J260" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="261" xml:space="preserve">
@@ -9609,7 +9609,7 @@
         <v>Pass</v>
       </c>
       <c r="J261" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="262" xml:space="preserve">
@@ -9644,7 +9644,7 @@
         <v>Pass</v>
       </c>
       <c r="J262" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="263" xml:space="preserve">
@@ -9679,7 +9679,7 @@
         <v>Pass</v>
       </c>
       <c r="J263" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="264" xml:space="preserve">
@@ -9714,7 +9714,7 @@
         <v>Pass</v>
       </c>
       <c r="J264" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="265" xml:space="preserve">
@@ -9749,7 +9749,7 @@
         <v>Pass</v>
       </c>
       <c r="J265" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="266" xml:space="preserve">
@@ -9784,7 +9784,7 @@
         <v>Pass</v>
       </c>
       <c r="J266" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="267" xml:space="preserve">
@@ -9819,7 +9819,7 @@
         <v>Pass</v>
       </c>
       <c r="J267" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="268" xml:space="preserve">
@@ -9854,7 +9854,7 @@
         <v>Pass</v>
       </c>
       <c r="J268" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="269" xml:space="preserve">
@@ -9889,7 +9889,7 @@
         <v>Pass</v>
       </c>
       <c r="J269" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="270" xml:space="preserve">
@@ -9924,7 +9924,7 @@
         <v>Pass</v>
       </c>
       <c r="J270" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="271" xml:space="preserve">
@@ -9959,7 +9959,7 @@
         <v>Pass</v>
       </c>
       <c r="J271" t="str">
-        <v>Localization bundle translations verified.</v>
+        <v>PASS — Localization bundle translations verified. Tamil and English strings render correctly on mobile.</v>
       </c>
     </row>
     <row r="272" xml:space="preserve">
